--- a/school-communication-platform/test-files/3-students.xlsx
+++ b/school-communication-platform/test-files/3-students.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t xml:space="preserve">Full Name</t>
   </si>
@@ -49,19 +49,16 @@
     <t xml:space="preserve">Emmanuel Kato</t>
   </si>
   <si>
-    <t xml:space="preserve">STU-2026-301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
+    <t xml:space="preserve">STU-2026-401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1,A</t>
   </si>
   <si>
     <t xml:space="preserve">Male</t>
   </si>
   <si>
-    <t xml:space="preserve">2010-02-14</t>
+    <t xml:space="preserve">2013-03-12</t>
   </si>
   <si>
     <t xml:space="preserve">John Kato</t>
@@ -82,16 +79,28 @@
     <t xml:space="preserve">2026-02-03</t>
   </si>
   <si>
+    <t xml:space="preserve">Joshua Wasswa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-07-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mukono</t>
+  </si>
+  <si>
     <t xml:space="preserve">Patricia Akello</t>
   </si>
   <si>
-    <t xml:space="preserve">STU-2026-302</t>
+    <t xml:space="preserve">STU-2026-403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1,B</t>
   </si>
   <si>
     <t xml:space="preserve">Female</t>
   </si>
   <si>
-    <t xml:space="preserve">2009-11-02</t>
+    <t xml:space="preserve">2013-11-02</t>
   </si>
   <si>
     <t xml:space="preserve">Margaret Akello</t>
@@ -106,34 +115,187 @@
     <t xml:space="preserve">Ntinda</t>
   </si>
   <si>
-    <t xml:space="preserve">Joshua Wasswa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010-05-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mukono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sarah Okello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STU-2024-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010-04-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. John Okello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+256700000020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parent@school.test</t>
+    <t xml:space="preserve">Derrick Mugisha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-01-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aisha Nansubuga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-2026-405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2,A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-04-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halima Nansubuga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+256700000062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">halima.n@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivan Ssemakula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-09-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entebbe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prossy Nabukenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-2026-407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2,B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rose Nabukenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+256700000063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenneth Opio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-02-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lydia Amoding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-2026-409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3,A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Amoding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+256700000064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">george.amoding@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mbale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felix Odongo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-12-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tororo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharon Atuhaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-2026-411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3,B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jennifer Atuhaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+256700000065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mbarara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hassan Kirumira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Tumusiime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-2026-413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4,A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-02-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charles Tumusiime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+256700000066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">charles.t@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grace Nalubega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masaka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pius Byaruhanga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STU-2026-415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4,B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-04-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joyce Byaruhanga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+256700000067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esther Namara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-12-12</t>
   </si>
 </sst>
 </file>
@@ -210,122 +372,398 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
       <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>33</v>
       </c>
       <c r="K4" t="s">
         <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>37</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="B6" t="s">
         <v>38</v>
       </c>
-      <c r="G5" t="s">
+      <c r="C6" t="s">
         <v>39</v>
       </c>
-      <c r="H5" t="s">
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
         <v>40</v>
       </c>
-      <c r="I5" t="s">
+      <c r="G6" t="s">
         <v>41</v>
       </c>
-      <c r="J5" t="s">
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" t="s">
         <v>21</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L6" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" t="s">
+        <v>73</v>
+      </c>
+      <c r="L12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" t="s">
+        <v>93</v>
+      </c>
+      <c r="L16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" t="s">
+        <v>95</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
